--- a/docs/spec.xlsx
+++ b/docs/spec.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amirdiaa/Desktop/Projects/RTL/CNN_FPGA/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08EEE793-34E8-6741-B33E-6114F1A38359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D4332C7-9755-5045-849E-0E9939DBA1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" xr2:uid="{6A45C92E-6DC1-6B4F-8548-B0A7ACA4743C}"/>
   </bookViews>
@@ -35,81 +35,102 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
   <si>
     <t>Parameter</t>
   </si>
   <si>
-    <t>Specification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Team Result </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Units </t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>Input image size</t>
-  </si>
-  <si>
     <t>Input precision</t>
   </si>
   <si>
-    <t>Kernel precision</t>
-  </si>
-  <si>
-    <t>Architecture type</t>
-  </si>
-  <si>
-    <t>Multipliers / MACs</t>
-  </si>
-  <si>
-    <t>Pipeline stages</t>
-  </si>
-  <si>
-    <t>Latency</t>
-  </si>
-  <si>
-    <t>Throughput</t>
-  </si>
-  <si>
-    <t>FPGA utilization</t>
-  </si>
-  <si>
-    <t>Maximum frequency</t>
-  </si>
-  <si>
-    <t>Power estimate</t>
-  </si>
-  <si>
-    <t>Verification status</t>
-  </si>
-  <si>
-    <t>FOM</t>
-  </si>
-  <si>
-    <t>32*32</t>
-  </si>
-  <si>
-    <t>8 bit wide</t>
-  </si>
-  <si>
-    <t>8-bit signed Fixed Point</t>
-  </si>
-  <si>
-    <t>Pipelined</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Output Precision </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 bit signed </t>
-  </si>
-  <si>
-    <t>8-bit usigned int</t>
+    <t>Future Improvement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decision </t>
+  </si>
+  <si>
+    <t>Kernal Size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3x3- Fixed </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variable </t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Standard for grayscale</t>
+  </si>
+  <si>
+    <t>Per Spec</t>
+  </si>
+  <si>
+    <t>Output precision</t>
+  </si>
+  <si>
+    <t>Kernal Precision</t>
+  </si>
+  <si>
+    <t>20 bits worst case, Extra bit for head room</t>
+  </si>
+  <si>
+    <t>Overflow/saturation handling</t>
+  </si>
+  <si>
+    <t>Saturation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleaner Implementation and more predictable behaviour </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Architecture </t>
+  </si>
+  <si>
+    <t>Buffering Scheme</t>
+  </si>
+  <si>
+    <t>Stride</t>
+  </si>
+  <si>
+    <t>Locked By spec</t>
+  </si>
+  <si>
+    <t>Border handling</t>
+  </si>
+  <si>
+    <t>No padding , valid Convolution</t>
+  </si>
+  <si>
+    <t>Kernel loading interface</t>
+  </si>
+  <si>
+    <t>write-enable + address + data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simple load interface </t>
+  </si>
+  <si>
+    <t xml:space="preserve">single-pixel-per-cycle output </t>
+  </si>
+  <si>
+    <t>2 Line buffers + Window gen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 Bit signed </t>
+  </si>
+  <si>
+    <t>8 bit signed integer</t>
+  </si>
+  <si>
+    <t>8 bit unsigned integer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Output Flow </t>
   </si>
 </sst>
 </file>
@@ -480,9 +501,10 @@
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -490,105 +512,154 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
+      <c r="C2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
+      <c r="A4" t="s">
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>13</v>
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>14</v>
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="A13" s="1"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="A14" s="1"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" t="s">
-        <v>23</v>
-      </c>
+      <c r="A16" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
